--- a/SportsCompUpdater/Sports_Comp_Updated.xlsx
+++ b/SportsCompUpdater/Sports_Comp_Updated.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="1740" windowWidth="28800" windowHeight="15940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -24,32 +24,38 @@
     </font>
     <font>
       <name val="Verdana"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Verdana"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color rgb="FF333333"/>
       <sz val="10"/>
     </font>
@@ -60,6 +66,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
@@ -70,12 +77,14 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF333333"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -128,9 +137,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -202,6 +211,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -583,16 +593,16 @@
   <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.1640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="32.6640625" customWidth="1" style="33" min="1" max="1"/>
-    <col width="4.5" customWidth="1" style="33" min="2" max="2"/>
-    <col width="12.1640625" customWidth="1" style="33" min="3" max="3"/>
-    <col width="11.1640625" customWidth="1" style="33" min="4" max="9"/>
-    <col width="13.1640625" customWidth="1" style="33" min="10" max="10"/>
-    <col width="11.6640625" customWidth="1" style="33" min="11" max="11"/>
-    <col width="11.1640625" customWidth="1" style="33" min="12" max="16"/>
+    <col width="32.6640625" customWidth="1" style="34" min="1" max="1"/>
+    <col width="4.5" customWidth="1" style="34" min="2" max="2"/>
+    <col width="12.1640625" customWidth="1" style="34" min="3" max="3"/>
+    <col width="11.1640625" customWidth="1" style="34" min="4" max="9"/>
+    <col width="13.1640625" customWidth="1" style="34" min="10" max="10"/>
+    <col width="11.6640625" customWidth="1" style="34" min="11" max="11"/>
+    <col width="11.1640625" customWidth="1" style="34" min="12" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" customHeight="1" s="33">
+    <row r="1" ht="14" customHeight="1" s="34">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Player</t>
@@ -674,7 +684,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13" customHeight="1" s="33">
+    <row r="2" ht="13" customHeight="1" s="34">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2025-26</t>
@@ -696,62 +706,56 @@
       <c r="O2" s="14" t="n"/>
       <c r="P2" s="14" t="n"/>
     </row>
-    <row r="3" ht="14" customHeight="1" s="33">
+    <row r="3" ht="14" customHeight="1" s="34">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>De'Aaaron Fox (G) - SAS</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="15">
-        <f>SUM(1336+327)</f>
-        <v/>
-      </c>
-      <c r="F3" s="16">
-        <f>SUM(270+79)</f>
-        <v/>
-      </c>
-      <c r="G3" s="17">
-        <f>SUM(445+125)</f>
-        <v/>
-      </c>
-      <c r="H3" s="16">
-        <f>SUM(19+9)</f>
-        <v/>
-      </c>
-      <c r="I3" s="17">
-        <f>SUM(89+27)</f>
-        <v/>
-      </c>
-      <c r="J3" s="18" t="n"/>
-      <c r="K3" s="19" t="n"/>
-      <c r="L3" s="17">
-        <f>SUM(131+30)</f>
-        <v/>
-      </c>
-      <c r="M3" s="17">
-        <f>SUM(1040+302)</f>
-        <v/>
-      </c>
-      <c r="N3" s="17">
-        <f>SUM(509+125)</f>
-        <v/>
-      </c>
-      <c r="O3" s="17">
-        <f>SUM(246+62)</f>
-        <v/>
-      </c>
-      <c r="P3" s="16">
-        <f>SUM(187+47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="14" customHeight="1" s="33">
+      <c r="E3" s="15" t="n">
+        <v>1663</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>349</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="J3" s="18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <v>161</v>
+      </c>
+      <c r="M3" s="17" t="n">
+        <v>1349</v>
+      </c>
+      <c r="N3" s="17" t="n">
+        <v>634</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <v>308</v>
+      </c>
+      <c r="P3" s="16" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1" s="34">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>Stephen Curry (G) - GSW</t>
+          <t>Stephen Curry</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -794,10 +798,10 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" ht="14" customHeight="1" s="33">
+    <row r="5" ht="14" customHeight="1" s="34">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>Zach Lavine (G) - SAC</t>
+          <t>Zach Lavine</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -840,10 +844,10 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" ht="14" customHeight="1" s="33">
+    <row r="6" ht="14" customHeight="1" s="34">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Jaylen Brown (F/G) - BOS</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -886,10 +890,10 @@
         <v>459</v>
       </c>
     </row>
-    <row r="7" ht="14" customHeight="1" s="33">
+    <row r="7" ht="14" customHeight="1" s="34">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Aaron Gordon (F) - DEN</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -932,10 +936,10 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1" s="33">
+    <row r="8" ht="14" customHeight="1" s="34">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Andre Drummond (C) - PHI</t>
+          <t>Andre Drummond</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -978,10 +982,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" ht="14" customHeight="1" s="33">
+    <row r="9" ht="14" customHeight="1" s="34">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Draymond Green (F) - GSW</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
@@ -1024,10 +1028,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" ht="14" customHeight="1" s="33">
+    <row r="10" ht="14" customHeight="1" s="34">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>D'Angelo Russell (G) - BKN</t>
+          <t>D'Angelo Russell</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -1070,10 +1074,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" ht="14" customHeight="1" s="33">
+    <row r="11" ht="14" customHeight="1" s="34">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns (C) - MIN</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1116,10 +1120,10 @@
         <v>427</v>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1" s="33">
+    <row r="12" ht="14" customHeight="1" s="34">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Domantas Sabonis (F/C) - SAC</t>
+          <t>Domantas Sabonis</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -1162,10 +1166,10 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1" s="33">
+    <row r="13" ht="14" customHeight="1" s="34">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Buddy Hield (G) - GSW</t>
+          <t>Buddy Hield</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -1208,10 +1212,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="14" customHeight="1" s="33">
+    <row r="14" ht="14" customHeight="1" s="34">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Brandon Ingram (F) - NOR</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
@@ -1254,10 +1258,10 @@
         <v>309</v>
       </c>
     </row>
-    <row r="15" ht="14" customHeight="1" s="33">
+    <row r="15" ht="14" customHeight="1" s="34">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Jayson Tatum (F/G) - BOS</t>
+          <t>Jayson Tatum</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
@@ -1300,10 +1304,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1" s="33">
+    <row r="16" ht="14" customHeight="1" s="34">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Bam Adebayo (C/F) - MIA</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
@@ -1346,10 +1350,10 @@
         <v>329</v>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1" s="33">
+    <row r="17" ht="14" customHeight="1" s="34">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>Mitchell Robinson (C) - NYK</t>
+          <t>Mitchell Robinson</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1392,10 +1396,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" ht="14" customHeight="1" s="33">
+    <row r="18" ht="14" customHeight="1" s="34">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Collin Sexton (G) - UTH</t>
+          <t>Collin Sexton</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
@@ -1438,10 +1442,10 @@
         <v>218</v>
       </c>
     </row>
-    <row r="19" ht="14" customHeight="1" s="33">
+    <row r="19" ht="14" customHeight="1" s="34">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Luka Doncic (G/F) - DAL</t>
+          <t>Luka Doncic</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1484,10 +1488,10 @@
         <v>503</v>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1" s="33">
+    <row r="20" ht="14" customHeight="1" s="34">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Miles Bridges (F) - CHA</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1530,10 +1534,10 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1" s="33">
+    <row r="21" ht="14" customHeight="1" s="34">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>Coby White (G) - CHI</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1576,10 +1580,10 @@
         <v>197</v>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1" s="33">
+    <row r="22" ht="14" customHeight="1" s="34">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Ja Morant (G) - MEM</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
@@ -1622,10 +1626,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1" s="33">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Anthony Edwards (G) - MIN</t>
+    <row r="23" ht="13" customHeight="1" s="34">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B23" s="26" t="n"/>
@@ -1668,10 +1672,10 @@
         <v>390</v>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1" s="33">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>Jalen Green (G) - HOU</t>
+    <row r="24" ht="13" customHeight="1" s="34">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B24" s="26" t="n"/>
@@ -1714,10 +1718,10 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" ht="13" customHeight="1" s="33">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Evan Mobley (F/C) - CLE</t>
+    <row r="25" ht="13" customHeight="1" s="34">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B25" s="26" t="n"/>
@@ -1760,10 +1764,10 @@
         <v>234</v>
       </c>
     </row>
-    <row r="26" ht="13" customHeight="1" s="33">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Jaden Ivey (G) - DET</t>
+    <row r="26" ht="13" customHeight="1" s="34">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Jaden Ivey</t>
         </is>
       </c>
       <c r="B26" s="26" t="n"/>
@@ -1806,10 +1810,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" ht="13" customHeight="1" s="33">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>Bennedict Mathurin (G) - IND</t>
+    <row r="27" ht="13" customHeight="1" s="34">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B27" s="26" t="n"/>
@@ -1852,10 +1856,10 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" ht="13" customHeight="1" s="33">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>Tyrese Maxey (G) - PHI</t>
+    <row r="28" ht="13" customHeight="1" s="34">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B28" s="26" t="n"/>
@@ -1898,10 +1902,10 @@
         <v>415</v>
       </c>
     </row>
-    <row r="29" ht="13" customHeight="1" s="33">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>Mark Williams (C) - CHA</t>
+    <row r="29" ht="13" customHeight="1" s="34">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>Mark Williams</t>
         </is>
       </c>
       <c r="B29" s="26" t="n"/>
@@ -1944,10 +1948,10 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" ht="13" customHeight="1" s="33">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>Jalen Brunson (G) - NYC</t>
+    <row r="30" ht="13" customHeight="1" s="34">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B30" s="26" t="n"/>
@@ -1990,10 +1994,10 @@
         <v>464</v>
       </c>
     </row>
-    <row r="31" ht="13" customHeight="1" s="33">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Amen Thompson (F) - HOU</t>
+    <row r="31" ht="13" customHeight="1" s="34">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="B31" s="26" t="n"/>
@@ -2036,10 +2040,10 @@
         <v>333</v>
       </c>
     </row>
-    <row r="32" ht="13" customHeight="1" s="33">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Ausar Thompson (F) - DET</t>
+    <row r="32" ht="13" customHeight="1" s="34">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B32" s="26" t="n"/>
@@ -2082,7 +2086,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1" s="33">
+    <row r="33" ht="13" customHeight="1" s="34">
       <c r="A33" s="26" t="inlineStr">
         <is>
           <t>Cam Thomas</t>
@@ -2128,7 +2132,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" ht="13" customHeight="1" s="33">
+    <row r="34" ht="13" customHeight="1" s="34">
       <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Derrick White</t>
@@ -2174,7 +2178,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="35" ht="13" customHeight="1" s="33">
+    <row r="35" ht="13" customHeight="1" s="34">
       <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Christian Braun</t>
@@ -2220,7 +2224,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" ht="13" customHeight="1" s="33">
+    <row r="36" ht="13" customHeight="1" s="34">
       <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
@@ -2266,7 +2270,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" ht="13" customHeight="1" s="33">
+    <row r="37" ht="13" customHeight="1" s="34">
       <c r="A37" s="26" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
@@ -2312,7 +2316,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="38" ht="13" customHeight="1" s="33">
+    <row r="38" ht="13" customHeight="1" s="34">
       <c r="A38" s="26" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
@@ -2358,7 +2362,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1" s="33">
+    <row r="39" ht="13" customHeight="1" s="34">
       <c r="A39" s="26" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
@@ -2404,7 +2408,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" ht="13" customHeight="1" s="33">
+    <row r="40" ht="13" customHeight="1" s="34">
       <c r="A40" s="26" t="inlineStr">
         <is>
           <t>Jeremiah Fears</t>
@@ -2450,7 +2454,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1" s="33">
+    <row r="41" ht="13" customHeight="1" s="34">
       <c r="A41" s="26" t="n"/>
       <c r="B41" s="26" t="n"/>
       <c r="C41" s="26" t="n"/>
@@ -2468,7 +2472,7 @@
       <c r="O41" s="26" t="n"/>
       <c r="P41" s="26" t="n"/>
     </row>
-    <row r="42" ht="13" customHeight="1" s="33">
+    <row r="42" ht="13" customHeight="1" s="34">
       <c r="A42" s="25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2526,7 +2530,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="13" customHeight="1" s="33">
+    <row r="43" ht="13" customHeight="1" s="34">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
@@ -2544,10 +2548,10 @@
       <c r="O43" s="8" t="n"/>
       <c r="P43" s="8" t="n"/>
     </row>
-    <row r="44" ht="14" customHeight="1" s="33">
+    <row r="44" ht="14" customHeight="1" s="34">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>Devin Booker (G) - PHX</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B44" s="5" t="n"/>
@@ -2590,10 +2594,10 @@
         <v>476</v>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1" s="33">
+    <row r="45" ht="14" customHeight="1" s="34">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>RJ Barrett - (G/F) - TOR</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
@@ -2636,10 +2640,10 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1" s="33">
+    <row r="46" ht="14" customHeight="1" s="34">
       <c r="A46" s="27" t="inlineStr">
         <is>
-          <t>James Harden (G) - PHI</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B46" s="5" t="n"/>
@@ -2682,10 +2686,10 @@
         <v>566</v>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1" s="33">
+    <row r="47" ht="14" customHeight="1" s="34">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>Bradley Beal (G) - PHX</t>
+          <t>Bradley Beal</t>
         </is>
       </c>
       <c r="B47" s="5" t="n"/>
@@ -2728,10 +2732,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1" s="33">
+    <row r="48" ht="14" customHeight="1" s="34">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>CJ McCollum (G) - NOR</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
@@ -2774,10 +2778,10 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1" s="33">
+    <row r="49" ht="14" customHeight="1" s="34">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>Joel Embiid (C) - PHI</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B49" s="5" t="n"/>
@@ -2820,10 +2824,10 @@
         <v>335</v>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1" s="33">
+    <row r="50" ht="14" customHeight="1" s="34">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>Julius Randle (F/C) - MIN</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B50" s="5" t="n"/>
@@ -2866,10 +2870,10 @@
         <v>446</v>
       </c>
     </row>
-    <row r="51" ht="14" customHeight="1" s="33">
+    <row r="51" ht="14" customHeight="1" s="34">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>Andrew Wiggins (F/G) - MIA</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B51" s="5" t="n"/>
@@ -2912,10 +2916,10 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" ht="14" customHeight="1" s="33">
+    <row r="52" ht="14" customHeight="1" s="34">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>Myles Turner (C) - IND</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B52" s="5" t="n"/>
@@ -2958,10 +2962,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1" s="33">
+    <row r="53" ht="14" customHeight="1" s="34">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>Pascal Siakam (F) - IND</t>
+          <t>Pascal Siakam</t>
         </is>
       </c>
       <c r="B53" s="5" t="n"/>
@@ -3004,10 +3008,10 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1" s="33">
+    <row r="54" ht="14" customHeight="1" s="34">
       <c r="A54" s="27" t="inlineStr">
         <is>
-          <t>Jamal Murray (G) - DEN</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B54" s="5" t="n"/>
@@ -3050,10 +3054,10 @@
         <v>385</v>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1" s="33">
+    <row r="55" ht="14" customHeight="1" s="34">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>Donovan Mitchell (G) - CLE</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B55" s="5" t="n"/>
@@ -3096,10 +3100,10 @@
         <v>447</v>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1" s="33">
+    <row r="56" ht="14" customHeight="1" s="34">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>Mikal Bridges (F) - BKN</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B56" s="5" t="n"/>
@@ -3142,10 +3146,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1" s="33">
+    <row r="57" ht="14" customHeight="1" s="34">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander (G) - OKC</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B57" s="5" t="n"/>
@@ -3188,10 +3192,10 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1" s="33">
+    <row r="58" ht="14" customHeight="1" s="34">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>Trae Young (G) - ATL</t>
+          <t>Trae Young</t>
         </is>
       </c>
       <c r="B58" s="5" t="n"/>
@@ -3234,10 +3238,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" ht="14" customHeight="1" s="33">
+    <row r="59" ht="14" customHeight="1" s="34">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>Jaren Jackson (F/C) - MEM</t>
+          <t>Jaren Jackson</t>
         </is>
       </c>
       <c r="B59" s="5" t="n"/>
@@ -3280,10 +3284,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1" s="33">
+    <row r="60" ht="14" customHeight="1" s="34">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>Michael Porter (F) - DEN</t>
+          <t>Michael Porter</t>
         </is>
       </c>
       <c r="B60" s="5" t="n"/>
@@ -3326,10 +3330,10 @@
         <v>195</v>
       </c>
     </row>
-    <row r="61" ht="14" customHeight="1" s="33">
+    <row r="61" ht="14" customHeight="1" s="34">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>Darius Garland (G) - CLE</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B61" s="5" t="n"/>
@@ -3372,10 +3376,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" ht="14" customHeight="1" s="33">
+    <row r="62" ht="14" customHeight="1" s="34">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>Tyler Herro (G) - MIA</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B62" s="5" t="n"/>
@@ -3418,10 +3422,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="63" ht="13" customHeight="1" s="33">
-      <c r="A63" s="26" t="inlineStr">
-        <is>
-          <t>Lamelo Ball (G) - CHA</t>
+    <row r="63" ht="13" customHeight="1" s="34">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>Lamelo Ball</t>
         </is>
       </c>
       <c r="B63" s="5" t="n"/>
@@ -3464,10 +3468,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="64" ht="13" customHeight="1" s="33">
-      <c r="A64" s="26" t="inlineStr">
-        <is>
-          <t>Onyeka Okongwu (F/C) - ATL</t>
+    <row r="64" ht="13" customHeight="1" s="34">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B64" s="5" t="n"/>
@@ -3510,10 +3514,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" ht="13" customHeight="1" s="33">
-      <c r="A65" s="26" t="inlineStr">
-        <is>
-          <t>Alperen Sengun (C) - HOU</t>
+    <row r="65" ht="13" customHeight="1" s="34">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>Alperen Sengun</t>
         </is>
       </c>
       <c r="B65" s="5" t="n"/>
@@ -3556,10 +3560,10 @@
         <v>289</v>
       </c>
     </row>
-    <row r="66" ht="13" customHeight="1" s="33">
-      <c r="A66" s="26" t="inlineStr">
-        <is>
-          <t>Josh Giddey (G/F) - CHI</t>
+    <row r="66" ht="13" customHeight="1" s="34">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>Josh Giddey</t>
         </is>
       </c>
       <c r="B66" s="5" t="n"/>
@@ -3602,10 +3606,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="67" ht="13" customHeight="1" s="33">
-      <c r="A67" s="26" t="inlineStr">
-        <is>
-          <t>Cade Cunningham (G/F) - DET</t>
+    <row r="67" ht="13" customHeight="1" s="34">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>Cade Cunningham</t>
         </is>
       </c>
       <c r="B67" s="5" t="n"/>
@@ -3648,10 +3652,10 @@
         <v>409</v>
       </c>
     </row>
-    <row r="68" ht="13" customHeight="1" s="33">
-      <c r="A68" s="26" t="inlineStr">
-        <is>
-          <t>Scottie Barnes (F) - TOR</t>
+    <row r="68" ht="13" customHeight="1" s="34">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B68" s="5" t="n"/>
@@ -3694,10 +3698,10 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" ht="13" customHeight="1" s="33">
-      <c r="A69" s="26" t="inlineStr">
-        <is>
-          <t>Jabari Smith (F) - HOU</t>
+    <row r="69" ht="13" customHeight="1" s="34">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>Jabari Smith</t>
         </is>
       </c>
       <c r="B69" s="5" t="n"/>
@@ -3740,10 +3744,10 @@
         <v>182</v>
       </c>
     </row>
-    <row r="70" ht="13" customHeight="1" s="33">
-      <c r="A70" s="26" t="inlineStr">
-        <is>
-          <t>Chet Holmgren (F) - OKC</t>
+    <row r="70" ht="13" customHeight="1" s="34">
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B70" s="5" t="n"/>
@@ -3786,10 +3790,10 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" ht="13" customHeight="1" s="33">
-      <c r="A71" s="26" t="inlineStr">
-        <is>
-          <t>Shaedon Sharpe (G) - POR</t>
+    <row r="71" ht="13" customHeight="1" s="34">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>Shaedon Sharpe</t>
         </is>
       </c>
       <c r="B71" s="5" t="n"/>
@@ -3832,10 +3836,10 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" ht="13" customHeight="1" s="33">
-      <c r="A72" s="26" t="inlineStr">
-        <is>
-          <t>Brandon Miller (F) - CHA</t>
+    <row r="72" ht="13" customHeight="1" s="34">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B72" s="5" t="n"/>
@@ -3878,7 +3882,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="73" ht="13" customHeight="1" s="33">
+    <row r="73" ht="13" customHeight="1" s="34">
       <c r="A73" s="26" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
@@ -3924,7 +3928,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="74" ht="13" customHeight="1" s="33">
+    <row r="74" ht="13" customHeight="1" s="34">
       <c r="A74" s="26" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
@@ -3970,7 +3974,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" ht="13" customHeight="1" s="33">
+    <row r="75" ht="13" customHeight="1" s="34">
       <c r="A75" s="26" t="inlineStr">
         <is>
           <t>Dereck Lively</t>
@@ -4016,7 +4020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" ht="13" customHeight="1" s="33">
+    <row r="76" ht="13" customHeight="1" s="34">
       <c r="A76" s="26" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
@@ -4062,7 +4066,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="77" ht="13" customHeight="1" s="33">
+    <row r="77" ht="13" customHeight="1" s="34">
       <c r="A77" s="26" t="inlineStr">
         <is>
           <t>Alex Sarr</t>
@@ -4108,7 +4112,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="78" ht="13" customHeight="1" s="33">
+    <row r="78" ht="13" customHeight="1" s="34">
       <c r="A78" s="26" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
@@ -4154,7 +4158,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79" ht="13" customHeight="1" s="33">
+    <row r="79" ht="13" customHeight="1" s="34">
       <c r="A79" s="26" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
@@ -4200,7 +4204,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="80" ht="13" customHeight="1" s="33">
+    <row r="80" ht="13" customHeight="1" s="34">
       <c r="A80" s="26" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
@@ -4246,53 +4250,24 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" ht="13" customHeight="1" s="33">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>Kon Knueppel</t>
-        </is>
-      </c>
+    <row r="81" ht="13" customHeight="1" s="34">
+      <c r="A81" s="26" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="5" t="n"/>
       <c r="D81" s="5" t="n"/>
-      <c r="E81" s="26" t="n">
-        <v>1498</v>
-      </c>
-      <c r="F81" s="26" t="n">
-        <v>432</v>
-      </c>
-      <c r="G81" s="26" t="n">
-        <v>274</v>
-      </c>
-      <c r="H81" s="26" t="n">
-        <v>19</v>
-      </c>
-      <c r="I81" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="J81" s="17" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="L81" s="26" t="n">
-        <v>273</v>
-      </c>
-      <c r="M81" s="26" t="n">
-        <v>1084</v>
-      </c>
-      <c r="N81" s="26" t="n">
-        <v>515</v>
-      </c>
-      <c r="O81" s="26" t="n">
-        <v>226</v>
-      </c>
-      <c r="P81" s="26" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" ht="13" customHeight="1" s="33">
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="L81" s="26" t="n"/>
+      <c r="M81" s="26" t="n"/>
+      <c r="N81" s="26" t="n"/>
+      <c r="O81" s="26" t="n"/>
+      <c r="P81" s="26" t="n"/>
+    </row>
+    <row r="82" ht="13" customHeight="1" s="34">
       <c r="A82" s="26" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="5" t="n"/>
@@ -4309,7 +4284,7 @@
       <c r="O82" s="26" t="n"/>
       <c r="P82" s="26" t="n"/>
     </row>
-    <row r="83" ht="13" customHeight="1" s="33">
+    <row r="83" ht="13" customHeight="1" s="34">
       <c r="A83" s="5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4367,7 +4342,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="13" customHeight="1" s="33">
+    <row r="84" ht="13" customHeight="1" s="34">
       <c r="A84" s="8" t="n"/>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
@@ -4385,7 +4360,7 @@
       <c r="O84" s="8" t="n"/>
       <c r="P84" s="8" t="n"/>
     </row>
-    <row r="85" ht="13" customHeight="1" s="33">
+    <row r="85" ht="13" customHeight="1" s="34">
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="5" t="n"/>
@@ -4403,7 +4378,7 @@
       <c r="O85" s="5" t="n"/>
       <c r="P85" s="5" t="n"/>
     </row>
-    <row r="86" ht="13" customHeight="1" s="33">
+    <row r="86" ht="13" customHeight="1" s="34">
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="5" t="n"/>
@@ -4421,7 +4396,7 @@
       <c r="O86" s="5" t="n"/>
       <c r="P86" s="5" t="n"/>
     </row>
-    <row r="87" ht="13" customHeight="1" s="33">
+    <row r="87" ht="13" customHeight="1" s="34">
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="5" t="n"/>
@@ -4439,7 +4414,7 @@
       <c r="O87" s="5" t="n"/>
       <c r="P87" s="5" t="n"/>
     </row>
-    <row r="88" ht="13" customHeight="1" s="33">
+    <row r="88" ht="13" customHeight="1" s="34">
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="5" t="n"/>
@@ -4457,7 +4432,7 @@
       <c r="O88" s="5" t="n"/>
       <c r="P88" s="5" t="n"/>
     </row>
-    <row r="89" ht="13" customHeight="1" s="33">
+    <row r="89" ht="13" customHeight="1" s="34">
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="5" t="n"/>
@@ -4475,7 +4450,7 @@
       <c r="O89" s="5" t="n"/>
       <c r="P89" s="5" t="n"/>
     </row>
-    <row r="90" ht="13" customHeight="1" s="33">
+    <row r="90" ht="13" customHeight="1" s="34">
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="5" t="n"/>
@@ -4493,7 +4468,7 @@
       <c r="O90" s="5" t="n"/>
       <c r="P90" s="5" t="n"/>
     </row>
-    <row r="91" ht="13" customHeight="1" s="33">
+    <row r="91" ht="13" customHeight="1" s="34">
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="5" t="n"/>
@@ -4511,7 +4486,7 @@
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="5" t="n"/>
     </row>
-    <row r="92" ht="13" customHeight="1" s="33">
+    <row r="92" ht="13" customHeight="1" s="34">
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="5" t="n"/>
@@ -4529,7 +4504,7 @@
       <c r="O92" s="5" t="n"/>
       <c r="P92" s="5" t="n"/>
     </row>
-    <row r="93" ht="13" customHeight="1" s="33">
+    <row r="93" ht="13" customHeight="1" s="34">
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="5" t="n"/>
@@ -4547,7 +4522,7 @@
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="5" t="n"/>
     </row>
-    <row r="94" ht="13" customHeight="1" s="33">
+    <row r="94" ht="13" customHeight="1" s="34">
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="5" t="n"/>
@@ -4565,7 +4540,7 @@
       <c r="O94" s="5" t="n"/>
       <c r="P94" s="5" t="n"/>
     </row>
-    <row r="95" ht="13" customHeight="1" s="33">
+    <row r="95" ht="13" customHeight="1" s="34">
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="5" t="n"/>
@@ -4583,7 +4558,7 @@
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="5" t="n"/>
     </row>
-    <row r="96" ht="13" customHeight="1" s="33">
+    <row r="96" ht="13" customHeight="1" s="34">
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="5" t="n"/>
@@ -4601,7 +4576,7 @@
       <c r="O96" s="5" t="n"/>
       <c r="P96" s="5" t="n"/>
     </row>
-    <row r="97" ht="13" customHeight="1" s="33">
+    <row r="97" ht="13" customHeight="1" s="34">
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="5" t="n"/>
@@ -4619,7 +4594,7 @@
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="5" t="n"/>
     </row>
-    <row r="98" ht="13" customHeight="1" s="33">
+    <row r="98" ht="13" customHeight="1" s="34">
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="5" t="n"/>
@@ -4637,7 +4612,7 @@
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="5" t="n"/>
     </row>
-    <row r="99" ht="13" customHeight="1" s="33">
+    <row r="99" ht="13" customHeight="1" s="34">
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="5" t="n"/>
@@ -4655,7 +4630,7 @@
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="5" t="n"/>
     </row>
-    <row r="100" ht="13" customHeight="1" s="33">
+    <row r="100" ht="13" customHeight="1" s="34">
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="5" t="n"/>
@@ -4673,7 +4648,7 @@
       <c r="O100" s="5" t="n"/>
       <c r="P100" s="5" t="n"/>
     </row>
-    <row r="101" ht="13" customHeight="1" s="33">
+    <row r="101" ht="13" customHeight="1" s="34">
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="5" t="n"/>
@@ -4691,7 +4666,7 @@
       <c r="O101" s="5" t="n"/>
       <c r="P101" s="5" t="n"/>
     </row>
-    <row r="102" ht="13" customHeight="1" s="33">
+    <row r="102" ht="13" customHeight="1" s="34">
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="5" t="n"/>
@@ -4709,7 +4684,7 @@
       <c r="O102" s="5" t="n"/>
       <c r="P102" s="5" t="n"/>
     </row>
-    <row r="103" ht="13" customHeight="1" s="33">
+    <row r="103" ht="13" customHeight="1" s="34">
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="5" t="n"/>
@@ -4727,7 +4702,7 @@
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="5" t="n"/>
     </row>
-    <row r="104" ht="13" customHeight="1" s="33">
+    <row r="104" ht="13" customHeight="1" s="34">
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="5" t="n"/>
@@ -4745,7 +4720,7 @@
       <c r="O104" s="5" t="n"/>
       <c r="P104" s="5" t="n"/>
     </row>
-    <row r="105" ht="13" customHeight="1" s="33">
+    <row r="105" ht="13" customHeight="1" s="34">
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="5" t="n"/>
@@ -4763,7 +4738,7 @@
       <c r="O105" s="5" t="n"/>
       <c r="P105" s="5" t="n"/>
     </row>
-    <row r="106" ht="13" customHeight="1" s="33">
+    <row r="106" ht="13" customHeight="1" s="34">
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="5" t="n"/>
@@ -4781,7 +4756,7 @@
       <c r="O106" s="5" t="n"/>
       <c r="P106" s="5" t="n"/>
     </row>
-    <row r="107" ht="13" customHeight="1" s="33">
+    <row r="107" ht="13" customHeight="1" s="34">
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="5" t="n"/>
@@ -4799,7 +4774,7 @@
       <c r="O107" s="5" t="n"/>
       <c r="P107" s="5" t="n"/>
     </row>
-    <row r="108" ht="13" customHeight="1" s="33">
+    <row r="108" ht="13" customHeight="1" s="34">
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="5" t="n"/>
@@ -4817,7 +4792,7 @@
       <c r="O108" s="5" t="n"/>
       <c r="P108" s="5" t="n"/>
     </row>
-    <row r="109" ht="13" customHeight="1" s="33">
+    <row r="109" ht="13" customHeight="1" s="34">
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="5" t="n"/>
